--- a/hospital/walls/hospital-walls.xlsx
+++ b/hospital/walls/hospital-walls.xlsx
@@ -4,29 +4,27 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="общий" sheetId="1" r:id="rId1"/>
     <sheet name="№1" sheetId="12" r:id="rId2"/>
     <sheet name="№2" sheetId="13" r:id="rId3"/>
     <sheet name="1.1.1" sheetId="9" r:id="rId4"/>
-    <sheet name="1.1.2" sheetId="5" r:id="rId5"/>
-    <sheet name="1.2.1" sheetId="2" r:id="rId6"/>
-    <sheet name="1.2.2" sheetId="3" r:id="rId7"/>
-    <sheet name="1.3.1" sheetId="4" r:id="rId8"/>
-    <sheet name="1.3.2" sheetId="7" r:id="rId9"/>
-    <sheet name="1.4.1" sheetId="6" r:id="rId10"/>
-    <sheet name="1.4.2" sheetId="10" r:id="rId11"/>
-    <sheet name="1.5.1" sheetId="8" r:id="rId12"/>
-    <sheet name="1.5.2" sheetId="11" r:id="rId13"/>
+    <sheet name="1.2.1" sheetId="2" r:id="rId5"/>
+    <sheet name="1.2.2" sheetId="3" r:id="rId6"/>
+    <sheet name="1.3.1" sheetId="4" r:id="rId7"/>
+    <sheet name="1.3.2" sheetId="7" r:id="rId8"/>
+    <sheet name="1.4.1" sheetId="6" r:id="rId9"/>
+    <sheet name="1.4.2" sheetId="10" r:id="rId10"/>
+    <sheet name="1.5.1" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="814">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -2327,9 +2325,6 @@
   </si>
   <si>
     <t>5 этаж</t>
-  </si>
-  <si>
-    <t>1-ое выполнение</t>
   </si>
   <si>
     <t xml:space="preserve">, 1эт, 2эт, 3эт, 4эт, 5эт. Перегородки Тип-4. Облицовка типа С626 на отнесенном металлическом каркасе толщиной 75 мм, с двуслойной обшивкой влагостойкими гипсокартнонными листами ГСП-H2 с одной стороны на одинарном металлическом каркасе из профилей ПН75x40 и ПС75х50, с внутренним заполнением минераловатной плитой толщиной 50 мм, плотностью 35-45 кг/м3, с индексом звукопоглащения 0,80 - 0,85 αw
@@ -2469,6 +2464,12 @@
   </si>
   <si>
     <t>Тип-5</t>
+  </si>
+  <si>
+    <t>Подв.</t>
+  </si>
+  <si>
+    <t>1 этаж</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2479,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2539,6 +2540,14 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF800000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
       <name val="ГОСТ тип А"/>
       <family val="2"/>
       <charset val="204"/>
@@ -2839,7 +2848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3045,6 +3054,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3492,7 +3510,9 @@
         <v>21</v>
       </c>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>812</v>
+      </c>
       <c r="L5" s="4">
         <v>1</v>
       </c>
@@ -3509,9 +3529,7 @@
         <v>5</v>
       </c>
       <c r="Q5" s="12"/>
-      <c r="R5" s="13" t="s">
-        <v>767</v>
-      </c>
+      <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="64" t="s">
@@ -5751,7 +5769,7 @@
         <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>46</v>
@@ -5943,7 +5961,7 @@
         <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>46</v>
@@ -6135,7 +6153,7 @@
         <v>44</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>46</v>
@@ -6327,7 +6345,7 @@
         <v>44</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>46</v>
@@ -7125,7 +7143,7 @@
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>46</v>
@@ -7412,7 +7430,7 @@
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>46</v>
@@ -7633,7 +7651,7 @@
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>46</v>
@@ -7770,7 +7788,7 @@
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>46</v>
@@ -7907,7 +7925,7 @@
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>46</v>
@@ -8044,7 +8062,7 @@
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>46</v>
@@ -8250,7 +8268,7 @@
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>57</v>
@@ -8319,7 +8337,7 @@
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>57</v>
@@ -8522,7 +8540,7 @@
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>57</v>
@@ -8592,7 +8610,7 @@
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>57</v>
@@ -8662,7 +8680,7 @@
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>57</v>
@@ -8732,7 +8750,7 @@
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>57</v>
@@ -8802,7 +8820,7 @@
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>57</v>
@@ -8872,7 +8890,7 @@
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>57</v>
@@ -9391,7 +9409,7 @@
         <v>289</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>46</v>
@@ -9788,7 +9806,7 @@
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>52</v>
@@ -10045,7 +10063,7 @@
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>46</v>
@@ -10678,7 +10696,7 @@
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>52</v>
@@ -10840,7 +10858,7 @@
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>52</v>
@@ -11002,7 +11020,7 @@
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>52</v>
@@ -11478,7 +11496,7 @@
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>46</v>
@@ -11640,7 +11658,7 @@
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>46</v>
@@ -12114,7 +12132,7 @@
       </c>
       <c r="D275" s="3"/>
       <c r="E275" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>46</v>
@@ -12276,7 +12294,7 @@
       </c>
       <c r="D280" s="3"/>
       <c r="E280" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>46</v>
@@ -12647,7 +12665,7 @@
         <v>440</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>46</v>
@@ -13162,7 +13180,7 @@
       </c>
       <c r="D308" s="3"/>
       <c r="E308" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>46</v>
@@ -13264,7 +13282,7 @@
       </c>
       <c r="D311" s="3"/>
       <c r="E311" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>46</v>
@@ -13523,7 +13541,7 @@
       </c>
       <c r="D319" s="3"/>
       <c r="E319" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>46</v>
@@ -13890,7 +13908,7 @@
       </c>
       <c r="D331" s="3"/>
       <c r="E331" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>46</v>
@@ -14147,7 +14165,7 @@
       </c>
       <c r="D339" s="3"/>
       <c r="E339" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>46</v>
@@ -14659,7 +14677,7 @@
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>46</v>
@@ -14761,7 +14779,7 @@
       </c>
       <c r="D358" s="3"/>
       <c r="E358" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>46</v>
@@ -14863,7 +14881,7 @@
       </c>
       <c r="D361" s="3"/>
       <c r="E361" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>46</v>
@@ -14965,7 +14983,7 @@
       </c>
       <c r="D364" s="3"/>
       <c r="E364" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>46</v>
@@ -15225,7 +15243,7 @@
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>46</v>
@@ -15295,7 +15313,7 @@
       </c>
       <c r="D374" s="3"/>
       <c r="E374" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>46</v>
@@ -15402,7 +15420,7 @@
       </c>
       <c r="D377" s="3"/>
       <c r="E377" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>46</v>
@@ -16452,7 +16470,7 @@
       </c>
       <c r="D411" s="3"/>
       <c r="E411" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>46</v>
@@ -17132,7 +17150,7 @@
       </c>
       <c r="D433" s="3"/>
       <c r="E433" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>46</v>
@@ -17509,7 +17527,7 @@
       </c>
       <c r="D445" s="3"/>
       <c r="E445" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>46</v>
@@ -17868,22 +17886,19 @@
       <c r="L457" s="8">
         <v>1342</v>
       </c>
-      <c r="M457" s="6">
+      <c r="M457" s="74">
         <v>1476</v>
       </c>
-      <c r="N457" s="8">
+      <c r="N457" s="74">
         <v>1550.4</v>
       </c>
-      <c r="O457" s="8">
+      <c r="O457" s="74">
         <v>1469.9</v>
       </c>
-      <c r="P457" s="9">
+      <c r="P457" s="76">
         <v>772.2</v>
       </c>
-      <c r="R457" s="61">
-        <f>SUM(M457:P457)</f>
-        <v>5268.5</v>
-      </c>
+      <c r="R457" s="61"/>
     </row>
     <row r="458" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="1" t="s">
@@ -17912,10 +17927,7 @@
       <c r="N458" s="9"/>
       <c r="O458" s="9"/>
       <c r="P458" s="9"/>
-      <c r="R458" s="61">
-        <f t="shared" ref="R458:R499" si="0">SUM(M458:P458)</f>
-        <v>0</v>
-      </c>
+      <c r="R458" s="61"/>
     </row>
     <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="1" t="s">
@@ -17944,10 +17956,7 @@
       <c r="N459" s="9"/>
       <c r="O459" s="9"/>
       <c r="P459" s="9"/>
-      <c r="R459" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R459" s="61"/>
     </row>
     <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="1" t="s">
@@ -17976,10 +17985,7 @@
       <c r="N460" s="9"/>
       <c r="O460" s="9"/>
       <c r="P460" s="9"/>
-      <c r="R460" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R460" s="61"/>
     </row>
     <row r="461" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="1" t="s">
@@ -18008,10 +18014,7 @@
       <c r="N461" s="9"/>
       <c r="O461" s="9"/>
       <c r="P461" s="9"/>
-      <c r="R461" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R461" s="61"/>
     </row>
     <row r="462" spans="1:18" ht="54" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="1" t="s">
@@ -18040,10 +18043,7 @@
       <c r="N462" s="9"/>
       <c r="O462" s="9"/>
       <c r="P462" s="9"/>
-      <c r="R462" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R462" s="61"/>
     </row>
     <row r="463" spans="1:18" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="1" t="s">
@@ -18080,22 +18080,19 @@
       <c r="L463" s="8">
         <v>0</v>
       </c>
-      <c r="M463" s="8">
+      <c r="M463" s="74">
         <v>45.8</v>
       </c>
-      <c r="N463" s="8">
+      <c r="N463" s="74">
         <v>45.5</v>
       </c>
-      <c r="O463" s="8">
+      <c r="O463" s="74">
         <v>46</v>
       </c>
-      <c r="P463" s="9">
+      <c r="P463" s="76">
         <v>25.1</v>
       </c>
-      <c r="R463" s="61">
-        <f t="shared" si="0"/>
-        <v>162.4</v>
-      </c>
+      <c r="R463" s="61"/>
     </row>
     <row r="464" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="1" t="s">
@@ -18124,10 +18121,7 @@
       <c r="N464" s="9"/>
       <c r="O464" s="9"/>
       <c r="P464" s="9"/>
-      <c r="R464" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R464" s="61"/>
     </row>
     <row r="465" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="1" t="s">
@@ -18156,10 +18150,7 @@
       <c r="N465" s="9"/>
       <c r="O465" s="9"/>
       <c r="P465" s="9"/>
-      <c r="R465" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R465" s="61"/>
     </row>
     <row r="466" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="1" t="s">
@@ -18188,10 +18179,7 @@
       <c r="N466" s="9"/>
       <c r="O466" s="9"/>
       <c r="P466" s="9"/>
-      <c r="R466" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R466" s="61"/>
     </row>
     <row r="467" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
@@ -18220,10 +18208,7 @@
       <c r="N467" s="9"/>
       <c r="O467" s="9"/>
       <c r="P467" s="9"/>
-      <c r="R467" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R467" s="61"/>
     </row>
     <row r="468" spans="1:18" ht="54" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="1" t="s">
@@ -18254,10 +18239,7 @@
       <c r="N468" s="9"/>
       <c r="O468" s="9"/>
       <c r="P468" s="9"/>
-      <c r="R468" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R468" s="61"/>
     </row>
     <row r="469" spans="1:18" ht="102" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
@@ -18304,10 +18286,7 @@
       <c r="P469" s="9">
         <v>38.700000000000003</v>
       </c>
-      <c r="R469" s="61">
-        <f t="shared" si="0"/>
-        <v>38.700000000000003</v>
-      </c>
+      <c r="R469" s="61"/>
     </row>
     <row r="470" spans="1:18" ht="54" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="1" t="s">
@@ -18336,10 +18315,7 @@
       <c r="N470" s="9"/>
       <c r="O470" s="9"/>
       <c r="P470" s="9"/>
-      <c r="R470" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R470" s="61"/>
     </row>
     <row r="471" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="1" t="s">
@@ -18368,10 +18344,7 @@
       <c r="N471" s="9"/>
       <c r="O471" s="9"/>
       <c r="P471" s="9"/>
-      <c r="R471" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R471" s="61"/>
     </row>
     <row r="472" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="1" t="s">
@@ -18400,10 +18373,7 @@
       <c r="N472" s="9"/>
       <c r="O472" s="9"/>
       <c r="P472" s="9"/>
-      <c r="R472" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R472" s="61"/>
     </row>
     <row r="473" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="1" t="s">
@@ -18432,10 +18402,7 @@
       <c r="N473" s="9"/>
       <c r="O473" s="9"/>
       <c r="P473" s="9"/>
-      <c r="R473" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R473" s="61"/>
     </row>
     <row r="474" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="1" t="s">
@@ -18464,10 +18431,7 @@
       <c r="N474" s="9"/>
       <c r="O474" s="9"/>
       <c r="P474" s="9"/>
-      <c r="R474" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R474" s="61"/>
     </row>
     <row r="475" spans="1:18" ht="158.55000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="1" t="s">
@@ -18483,7 +18447,7 @@
         <v>753</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>46</v>
@@ -18504,22 +18468,19 @@
       <c r="L475" s="8">
         <v>186.2</v>
       </c>
-      <c r="M475" s="8">
+      <c r="M475" s="74">
         <v>85.2</v>
       </c>
-      <c r="N475" s="8">
+      <c r="N475" s="74">
         <v>102</v>
       </c>
-      <c r="O475" s="8">
+      <c r="O475" s="74">
         <v>140.19999999999999</v>
       </c>
       <c r="P475" s="9">
         <v>61.6</v>
       </c>
-      <c r="R475" s="61">
-        <f t="shared" si="0"/>
-        <v>389</v>
-      </c>
+      <c r="R475" s="61"/>
     </row>
     <row r="476" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="1" t="s">
@@ -18548,10 +18509,7 @@
       <c r="N476" s="9"/>
       <c r="O476" s="9"/>
       <c r="P476" s="9"/>
-      <c r="R476" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R476" s="61"/>
     </row>
     <row r="477" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="1" t="s">
@@ -18580,10 +18538,7 @@
       <c r="N477" s="9"/>
       <c r="O477" s="9"/>
       <c r="P477" s="9"/>
-      <c r="R477" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R477" s="61"/>
     </row>
     <row r="478" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="1" t="s">
@@ -18612,10 +18567,7 @@
       <c r="N478" s="9"/>
       <c r="O478" s="9"/>
       <c r="P478" s="9"/>
-      <c r="R478" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R478" s="61"/>
     </row>
     <row r="479" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
@@ -18644,10 +18596,7 @@
       <c r="N479" s="9"/>
       <c r="O479" s="9"/>
       <c r="P479" s="9"/>
-      <c r="R479" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R479" s="61"/>
     </row>
     <row r="480" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
@@ -18676,10 +18625,7 @@
       <c r="N480" s="9"/>
       <c r="O480" s="9"/>
       <c r="P480" s="9"/>
-      <c r="R480" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R480" s="61"/>
     </row>
     <row r="481" spans="1:18" ht="153" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
@@ -18714,22 +18660,19 @@
       <c r="L481" s="8">
         <v>18.100000000000001</v>
       </c>
-      <c r="M481" s="8">
+      <c r="M481" s="6">
         <v>22.2</v>
       </c>
-      <c r="N481" s="8">
+      <c r="N481" s="6">
         <v>22.2</v>
       </c>
-      <c r="O481" s="8">
+      <c r="O481" s="6">
         <v>22.2</v>
       </c>
       <c r="P481" s="9">
         <v>11.1</v>
       </c>
-      <c r="R481" s="61">
-        <f t="shared" si="0"/>
-        <v>77.699999999999989</v>
-      </c>
+      <c r="R481" s="61"/>
     </row>
     <row r="482" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="1" t="s">
@@ -18758,10 +18701,7 @@
       <c r="N482" s="9"/>
       <c r="O482" s="9"/>
       <c r="P482" s="9"/>
-      <c r="R482" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R482" s="61"/>
     </row>
     <row r="483" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="1" t="s">
@@ -18790,10 +18730,7 @@
       <c r="N483" s="9"/>
       <c r="O483" s="9"/>
       <c r="P483" s="9"/>
-      <c r="R483" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R483" s="61"/>
     </row>
     <row r="484" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="1" t="s">
@@ -18822,10 +18759,7 @@
       <c r="N484" s="9"/>
       <c r="O484" s="9"/>
       <c r="P484" s="9"/>
-      <c r="R484" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R484" s="61"/>
     </row>
     <row r="485" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="1" t="s">
@@ -18854,10 +18788,7 @@
       <c r="N485" s="9"/>
       <c r="O485" s="9"/>
       <c r="P485" s="9"/>
-      <c r="R485" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R485" s="61"/>
     </row>
     <row r="486" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="1" t="s">
@@ -18886,10 +18817,7 @@
       <c r="N486" s="9"/>
       <c r="O486" s="9"/>
       <c r="P486" s="9"/>
-      <c r="R486" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R486" s="61"/>
     </row>
     <row r="487" spans="1:18" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
@@ -18905,7 +18833,7 @@
         <v>755</v>
       </c>
       <c r="E487" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>46</v>
@@ -18926,22 +18854,19 @@
       <c r="L487" s="8">
         <v>18.3</v>
       </c>
-      <c r="M487" s="8">
+      <c r="M487" s="74">
         <v>17.8</v>
       </c>
-      <c r="N487" s="8">
+      <c r="N487" s="74">
         <v>16.100000000000001</v>
       </c>
-      <c r="O487" s="8">
+      <c r="O487" s="74">
         <v>23.7</v>
       </c>
       <c r="P487" s="9">
         <v>32.200000000000003</v>
       </c>
-      <c r="R487" s="61">
-        <f t="shared" si="0"/>
-        <v>89.800000000000011</v>
-      </c>
+      <c r="R487" s="61"/>
     </row>
     <row r="488" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
@@ -18970,10 +18895,7 @@
       <c r="N488" s="9"/>
       <c r="O488" s="9"/>
       <c r="P488" s="9"/>
-      <c r="R488" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R488" s="61"/>
     </row>
     <row r="489" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
@@ -19002,10 +18924,7 @@
       <c r="N489" s="9"/>
       <c r="O489" s="9"/>
       <c r="P489" s="9"/>
-      <c r="R489" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R489" s="61"/>
     </row>
     <row r="490" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
@@ -19034,10 +18953,7 @@
       <c r="N490" s="9"/>
       <c r="O490" s="9"/>
       <c r="P490" s="9"/>
-      <c r="R490" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R490" s="61"/>
     </row>
     <row r="491" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
@@ -19066,10 +18982,7 @@
       <c r="N491" s="9"/>
       <c r="O491" s="9"/>
       <c r="P491" s="9"/>
-      <c r="R491" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R491" s="61"/>
     </row>
     <row r="492" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="1" t="s">
@@ -19100,10 +19013,7 @@
       <c r="N492" s="9"/>
       <c r="O492" s="9"/>
       <c r="P492" s="9"/>
-      <c r="R492" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R492" s="61"/>
     </row>
     <row r="493" spans="1:18" ht="211.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="1" t="s">
@@ -19119,7 +19029,7 @@
         <v>756</v>
       </c>
       <c r="E493" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>46</v>
@@ -19140,22 +19050,19 @@
       <c r="L493" s="8">
         <v>48.8</v>
       </c>
-      <c r="M493" s="8">
+      <c r="M493" s="74">
         <v>46.4</v>
       </c>
-      <c r="N493" s="8">
+      <c r="N493" s="74">
         <v>48.1</v>
       </c>
-      <c r="O493" s="8">
+      <c r="O493" s="74">
         <v>25.5</v>
       </c>
       <c r="P493" s="9">
         <v>8.1999999999999993</v>
       </c>
-      <c r="R493" s="61">
-        <f t="shared" si="0"/>
-        <v>128.19999999999999</v>
-      </c>
+      <c r="R493" s="61"/>
     </row>
     <row r="494" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="1" t="s">
@@ -19180,14 +19087,11 @@
       <c r="J494" s="25"/>
       <c r="K494" s="29"/>
       <c r="L494" s="9"/>
-      <c r="M494" s="23"/>
-      <c r="N494" s="9"/>
-      <c r="O494" s="9"/>
+      <c r="M494" s="75"/>
+      <c r="N494" s="76"/>
+      <c r="O494" s="76"/>
       <c r="P494" s="9"/>
-      <c r="R494" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R494" s="61"/>
     </row>
     <row r="495" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
@@ -19212,14 +19116,11 @@
       <c r="J495" s="25"/>
       <c r="K495" s="29"/>
       <c r="L495" s="9"/>
-      <c r="M495" s="23"/>
-      <c r="N495" s="9"/>
-      <c r="O495" s="9"/>
+      <c r="M495" s="75"/>
+      <c r="N495" s="76"/>
+      <c r="O495" s="76"/>
       <c r="P495" s="9"/>
-      <c r="R495" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R495" s="61"/>
     </row>
     <row r="496" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
@@ -19244,14 +19145,11 @@
       <c r="J496" s="25"/>
       <c r="K496" s="29"/>
       <c r="L496" s="9"/>
-      <c r="M496" s="23"/>
-      <c r="N496" s="9"/>
-      <c r="O496" s="9"/>
+      <c r="M496" s="75"/>
+      <c r="N496" s="76"/>
+      <c r="O496" s="76"/>
       <c r="P496" s="9"/>
-      <c r="R496" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R496" s="61"/>
     </row>
     <row r="497" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
@@ -19276,14 +19174,11 @@
       <c r="J497" s="25"/>
       <c r="K497" s="29"/>
       <c r="L497" s="9"/>
-      <c r="M497" s="23"/>
-      <c r="N497" s="9"/>
-      <c r="O497" s="9"/>
+      <c r="M497" s="75"/>
+      <c r="N497" s="76"/>
+      <c r="O497" s="76"/>
       <c r="P497" s="9"/>
-      <c r="R497" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R497" s="61"/>
     </row>
     <row r="498" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="1" t="s">
@@ -19308,14 +19203,11 @@
       <c r="J498" s="25"/>
       <c r="K498" s="29"/>
       <c r="L498" s="9"/>
-      <c r="M498" s="23"/>
-      <c r="N498" s="9"/>
-      <c r="O498" s="9"/>
+      <c r="M498" s="75"/>
+      <c r="N498" s="76"/>
+      <c r="O498" s="76"/>
       <c r="P498" s="9"/>
-      <c r="R498" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R498" s="61"/>
     </row>
     <row r="499" spans="1:18" ht="168" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="1" t="s">
@@ -19328,10 +19220,10 @@
         <v>98</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>46</v>
@@ -19352,22 +19244,19 @@
       <c r="L499" s="8">
         <v>525.20000000000005</v>
       </c>
-      <c r="M499" s="8">
+      <c r="M499" s="74">
         <v>520.1</v>
       </c>
-      <c r="N499" s="8">
+      <c r="N499" s="74">
         <v>520.79999999999995</v>
       </c>
-      <c r="O499" s="8">
+      <c r="O499" s="74">
         <v>510.4</v>
       </c>
       <c r="P499" s="9">
         <v>307.2</v>
       </c>
-      <c r="R499" s="61">
-        <f t="shared" si="0"/>
-        <v>1858.5000000000002</v>
-      </c>
+      <c r="R499" s="61"/>
     </row>
     <row r="500" spans="1:18" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
@@ -19571,7 +19460,7 @@
         <v>440</v>
       </c>
       <c r="E507" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>46</v>
@@ -19797,7 +19686,7 @@
       </c>
       <c r="D515" s="3"/>
       <c r="E515" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>46</v>
@@ -19845,7 +19734,7 @@
       <c r="O516" s="9"/>
       <c r="P516" s="9"/>
     </row>
-    <row r="517" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>740</v>
       </c>
@@ -19887,7 +19776,7 @@
       </c>
       <c r="D518" s="3"/>
       <c r="E518" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>46</v>
@@ -19907,7 +19796,7 @@
       <c r="O518" s="8"/>
       <c r="P518" s="9"/>
     </row>
-    <row r="519" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>742</v>
       </c>
@@ -19977,7 +19866,7 @@
       </c>
       <c r="D521" s="3"/>
       <c r="E521" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>46</v>
@@ -20210,7 +20099,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
@@ -20242,124 +20131,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A2" s="42">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F2" s="8">
-        <v>1463.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>45.08</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>138.798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>22.989000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>25.245000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>500.19199999999995</v>
+        <v>21.756</v>
       </c>
     </row>
   </sheetData>
@@ -20369,6 +20158,1047 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" style="20" customWidth="1"/>
+    <col min="2" max="2" width="48.88671875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="62.21875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>764.47800000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>24.849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>60.984000000000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>8.0359999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>301.05599999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>31.234000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>37.539000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="8">
+        <v>10.767000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="9" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>763</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>764</v>
+      </c>
+      <c r="I1" s="60" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f>SUM(G2:I2)</f>
+        <v>4460.3999999999996</v>
+      </c>
+      <c r="G2" s="59">
+        <v>1454</v>
+      </c>
+      <c r="H2" s="59">
+        <v>1542.5</v>
+      </c>
+      <c r="I2" s="59">
+        <v>1463.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <f>SUM(G3:I3)</f>
+        <v>134.09899999999999</v>
+      </c>
+      <c r="G3" s="8">
+        <v>44.883999999999993</v>
+      </c>
+      <c r="H3" s="8">
+        <v>44.134999999999998</v>
+      </c>
+      <c r="I3" s="8">
+        <v>45.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F7" si="0">SUM(G4:J4)</f>
+        <v>322.42200000000003</v>
+      </c>
+      <c r="G4" s="8">
+        <v>82.644000000000005</v>
+      </c>
+      <c r="H4" s="8">
+        <v>100.98</v>
+      </c>
+      <c r="I4" s="8">
+        <v>138.798</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="0"/>
+        <v>56.38900000000001</v>
+      </c>
+      <c r="G5" s="8">
+        <v>17.622</v>
+      </c>
+      <c r="H5" s="8">
+        <v>15.778000000000002</v>
+      </c>
+      <c r="I5" s="8">
+        <v>22.989000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="0"/>
+        <v>118.31900000000002</v>
+      </c>
+      <c r="G6" s="8">
+        <v>45.936</v>
+      </c>
+      <c r="H6" s="8">
+        <v>47.138000000000005</v>
+      </c>
+      <c r="I6" s="8">
+        <v>25.245000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="0"/>
+        <v>1530.683</v>
+      </c>
+      <c r="G7" s="8">
+        <v>514.899</v>
+      </c>
+      <c r="H7" s="8">
+        <v>515.59199999999998</v>
+      </c>
+      <c r="I7" s="8">
+        <v>500.19199999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="8" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>813</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f>SUM(G2:H2)</f>
+        <v>2106.4780000000001</v>
+      </c>
+      <c r="G2" s="59">
+        <v>1342</v>
+      </c>
+      <c r="H2" s="59">
+        <v>764.47800000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>24.849</v>
+      </c>
+      <c r="G3" s="59">
+        <v>0</v>
+      </c>
+      <c r="H3" s="59">
+        <v>24.849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="59">
+        <f t="shared" ref="F4:F9" si="0">SUM(G4:H4)</f>
+        <v>247.184</v>
+      </c>
+      <c r="G4" s="8">
+        <v>186.2</v>
+      </c>
+      <c r="H4" s="8">
+        <v>60.984000000000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="59">
+        <f t="shared" si="0"/>
+        <v>56.835999999999999</v>
+      </c>
+      <c r="G5" s="8">
+        <v>48.8</v>
+      </c>
+      <c r="H5" s="8">
+        <v>8.0359999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="59">
+        <f>SUM(G6:H6)</f>
+        <v>826.25600000000009</v>
+      </c>
+      <c r="G6" s="8">
+        <v>525.20000000000005</v>
+      </c>
+      <c r="H6" s="8">
+        <v>301.05599999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="59">
+        <f>SUM(G7:H7)</f>
+        <v>49.534000000000006</v>
+      </c>
+      <c r="G7" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="H7" s="8">
+        <v>31.234000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="59">
+        <f t="shared" si="0"/>
+        <v>58.639000000000003</v>
+      </c>
+      <c r="G8" s="8">
+        <v>21.1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>37.539000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="59">
+        <f t="shared" si="0"/>
+        <v>28.867000000000004</v>
+      </c>
+      <c r="G9" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H9" s="8">
+        <v>10.767000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="44.88671875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="61.88671875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>186.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>525.20000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>44.883999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>82.644000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>17.622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>45.936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>514.899</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -20419,7 +21249,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="8">
-        <v>21.756</v>
+        <v>21.9</v>
       </c>
     </row>
   </sheetData>
@@ -20428,8 +21258,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -20479,7 +21312,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="8">
-        <v>764.47800000000007</v>
+        <v>1542.5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -20499,7 +21332,7 @@
         <v>46</v>
       </c>
       <c r="F3" s="8">
-        <v>24.849</v>
+        <v>44.134999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -20513,13 +21346,13 @@
         <v>753</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="8">
-        <v>60.984000000000009</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -20533,13 +21366,13 @@
         <v>755</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="8">
-        <v>31.234000000000002</v>
+        <v>15.778000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -20553,13 +21386,13 @@
         <v>756</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="8">
-        <v>8.0359999999999996</v>
+        <v>47.138000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -20570,16 +21403,16 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="8">
-        <v>301.05599999999998</v>
+        <v>515.59199999999998</v>
       </c>
     </row>
   </sheetData>
@@ -20588,810 +21421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>37.539000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>10.767000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="9" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>763</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>764</v>
-      </c>
-      <c r="I1" s="60" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <f>SUM(G2:I2)</f>
-        <v>4460.3999999999996</v>
-      </c>
-      <c r="G2" s="59">
-        <v>1454</v>
-      </c>
-      <c r="H2" s="59">
-        <v>1542.5</v>
-      </c>
-      <c r="I2" s="59">
-        <v>1463.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <f>SUM(G3:I3)</f>
-        <v>134.09899999999999</v>
-      </c>
-      <c r="G3" s="8">
-        <v>44.883999999999993</v>
-      </c>
-      <c r="H3" s="8">
-        <v>44.134999999999998</v>
-      </c>
-      <c r="I3" s="8">
-        <v>45.08</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="10" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>763</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>764</v>
-      </c>
-      <c r="I1" s="60" t="s">
-        <v>765</v>
-      </c>
-      <c r="J1" s="60" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <f>SUM(G2:J2)</f>
-        <v>764.47800000000007</v>
-      </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59">
-        <v>764.47800000000007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <f>SUM(G3:J3)</f>
-        <v>24.849</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8">
-        <v>24.849</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <f>SUM(G4:J4)</f>
-        <v>383.40600000000006</v>
-      </c>
-      <c r="G4" s="8">
-        <v>82.644000000000005</v>
-      </c>
-      <c r="H4" s="8">
-        <v>100.98</v>
-      </c>
-      <c r="I4" s="8">
-        <v>138.798</v>
-      </c>
-      <c r="J4" s="8">
-        <v>60.984000000000009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <f>SUM(G5:J5)</f>
-        <v>87.623000000000019</v>
-      </c>
-      <c r="G5" s="8">
-        <v>17.622</v>
-      </c>
-      <c r="H5" s="8">
-        <v>15.778000000000002</v>
-      </c>
-      <c r="I5" s="8">
-        <v>22.989000000000001</v>
-      </c>
-      <c r="J5" s="8">
-        <v>31.234000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <f>SUM(G6:J6)</f>
-        <v>126.35500000000002</v>
-      </c>
-      <c r="G6" s="8">
-        <v>45.936</v>
-      </c>
-      <c r="H6" s="8">
-        <v>47.138000000000005</v>
-      </c>
-      <c r="I6" s="8">
-        <v>25.245000000000001</v>
-      </c>
-      <c r="J6" s="8">
-        <v>8.0359999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <f>SUM(G7:J7)</f>
-        <v>1831.739</v>
-      </c>
-      <c r="G7" s="8">
-        <v>514.899</v>
-      </c>
-      <c r="H7" s="8">
-        <v>515.59199999999998</v>
-      </c>
-      <c r="I7" s="8">
-        <v>500.19199999999995</v>
-      </c>
-      <c r="J7" s="8">
-        <v>301.05599999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>186.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>525.20000000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>44.883999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>82.644000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>17.622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>45.936</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>514.899</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -21442,7 +21472,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="8">
-        <v>21.9</v>
+        <v>21.756</v>
       </c>
     </row>
   </sheetData>
@@ -21451,8 +21481,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -21502,7 +21535,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="8">
-        <v>1542.5</v>
+        <v>1463.9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -21522,7 +21555,7 @@
         <v>46</v>
       </c>
       <c r="F3" s="8">
-        <v>44.134999999999998</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -21536,13 +21569,13 @@
         <v>753</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="8">
-        <v>100.98</v>
+        <v>138.798</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -21556,13 +21589,13 @@
         <v>755</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="8">
-        <v>15.778000000000002</v>
+        <v>22.989000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -21576,13 +21609,13 @@
         <v>756</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="8">
-        <v>47.138000000000005</v>
+        <v>25.245000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
@@ -21593,76 +21626,16 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="8">
-        <v>515.59199999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>21.756</v>
+        <v>500.19199999999995</v>
       </c>
     </row>
   </sheetData>
